--- a/LoanOfficer-A/2023/147 sheenarani.xlsx
+++ b/LoanOfficer-A/2023/147 sheenarani.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="G2" s="21">
         <f>B3+G1-1</f>
-        <v>119</v>
+        <v>46100</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>24000</v>
+        <v>22400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -874,9 +874,15 @@
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="1"/>
+      <c r="B3" s="3">
+        <v>45981</v>
+      </c>
+      <c r="C3" s="4">
+        <v>200</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
       <c r="E3" s="1">
         <v>31</v>
       </c>
@@ -900,9 +906,15 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="1"/>
+      <c r="B4" s="3">
+        <v>45981</v>
+      </c>
+      <c r="C4" s="4">
+        <v>200</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
       <c r="E4" s="1">
         <v>32</v>
       </c>
@@ -926,9 +938,15 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="3">
+        <v>45983</v>
+      </c>
+      <c r="C5" s="4">
+        <v>200</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
       <c r="E5" s="1">
         <v>33</v>
       </c>
@@ -952,9 +970,15 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="3">
+        <v>45983</v>
+      </c>
+      <c r="C6" s="4">
+        <v>200</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1">
         <v>34</v>
       </c>
@@ -978,9 +1002,15 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="3">
+        <v>45983</v>
+      </c>
+      <c r="C7" s="4">
+        <v>200</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1">
         <v>35</v>
       </c>
@@ -1004,9 +1034,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>45983</v>
+      </c>
+      <c r="C8" s="4">
+        <v>200</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>
@@ -1030,9 +1066,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>45985</v>
+      </c>
+      <c r="C9" s="4">
+        <v>200</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>
@@ -1056,9 +1098,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>45985</v>
+      </c>
+      <c r="C10" s="4">
+        <v>200</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>

--- a/LoanOfficer-A/2023/147 sheenarani.xlsx
+++ b/LoanOfficer-A/2023/147 sheenarani.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>1600</v>
+        <v>4400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>22400</v>
+        <v>19600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1130,9 +1130,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>45991</v>
+      </c>
+      <c r="C11" s="4">
+        <v>200</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>
@@ -1156,9 +1162,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>45991</v>
+      </c>
+      <c r="C12" s="4">
+        <v>200</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>
@@ -1182,9 +1194,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>45991</v>
+      </c>
+      <c r="C13" s="4">
+        <v>200</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
@@ -1208,9 +1226,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>45991</v>
+      </c>
+      <c r="C14" s="4">
+        <v>200</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1234,9 +1258,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45991</v>
+      </c>
+      <c r="C15" s="4">
+        <v>200</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>
@@ -1260,9 +1290,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45997</v>
+      </c>
+      <c r="C16" s="4">
+        <v>200</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
@@ -1286,9 +1322,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45997</v>
+      </c>
+      <c r="C17" s="4">
+        <v>200</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>
@@ -1312,9 +1354,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>45997</v>
+      </c>
+      <c r="C18" s="4">
+        <v>200</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>
@@ -1338,9 +1386,15 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>45997</v>
+      </c>
+      <c r="C19" s="4">
+        <v>200</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>
@@ -1364,9 +1418,15 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="3">
+        <v>45997</v>
+      </c>
+      <c r="C20" s="4">
+        <v>200</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
       <c r="E20" s="1">
         <v>48</v>
       </c>
@@ -1390,9 +1450,15 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
+      <c r="B21" s="3">
+        <v>45997</v>
+      </c>
+      <c r="C21" s="4">
+        <v>200</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
       <c r="E21" s="1">
         <v>49</v>
       </c>
@@ -1416,9 +1482,15 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="3">
+        <v>45997</v>
+      </c>
+      <c r="C22" s="4">
+        <v>200</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
@@ -1442,9 +1514,15 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
+      <c r="B23" s="3">
+        <v>45997</v>
+      </c>
+      <c r="C23" s="4">
+        <v>200</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
       <c r="E23" s="1">
         <v>51</v>
       </c>
@@ -1468,9 +1546,15 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="3">
+        <v>45997</v>
+      </c>
+      <c r="C24" s="4">
+        <v>200</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
       <c r="E24" s="1">
         <v>52</v>
       </c>

--- a/LoanOfficer-A/2023/147 sheenarani.xlsx
+++ b/LoanOfficer-A/2023/147 sheenarani.xlsx
@@ -775,7 +775,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P94"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" customWidth="1"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>4400</v>
+        <v>5600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>19600</v>
+        <v>18400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1578,9 +1578,15 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="3">
+        <v>46006</v>
+      </c>
+      <c r="C25" s="4">
+        <v>200</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
       <c r="E25" s="1">
         <v>53</v>
       </c>
@@ -1604,9 +1610,15 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="3">
+        <v>46006</v>
+      </c>
+      <c r="C26" s="4">
+        <v>200</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
       <c r="E26" s="1">
         <v>54</v>
       </c>
@@ -1630,9 +1642,15 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="3">
+        <v>46006</v>
+      </c>
+      <c r="C27" s="4">
+        <v>200</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
       <c r="E27" s="1">
         <v>55</v>
       </c>
@@ -1656,9 +1674,15 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="3">
+        <v>46006</v>
+      </c>
+      <c r="C28" s="4">
+        <v>200</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
       <c r="E28" s="1">
         <v>56</v>
       </c>
@@ -1682,9 +1706,15 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="3">
+        <v>46006</v>
+      </c>
+      <c r="C29" s="4">
+        <v>200</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
       <c r="E29" s="1">
         <v>57</v>
       </c>
@@ -1708,9 +1738,15 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="3">
+        <v>46006</v>
+      </c>
+      <c r="C30" s="4">
+        <v>200</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
       <c r="E30" s="1">
         <v>58</v>
       </c>
@@ -1781,1030 +1817,6 @@
       <c r="N32" s="1"/>
       <c r="O32" s="4"/>
       <c r="P32" s="1"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
-        <v>121</v>
-      </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1">
-        <v>151</v>
-      </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1">
-        <v>181</v>
-      </c>
-      <c r="J34" s="1"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1">
-        <v>211</v>
-      </c>
-      <c r="N34" s="1"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="1"/>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
-        <v>122</v>
-      </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1">
-        <v>152</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1">
-        <v>182</v>
-      </c>
-      <c r="J35" s="1"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1">
-        <v>212</v>
-      </c>
-      <c r="N35" s="1"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="1"/>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
-        <v>123</v>
-      </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1">
-        <v>153</v>
-      </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1">
-        <v>183</v>
-      </c>
-      <c r="J36" s="1"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1">
-        <v>213</v>
-      </c>
-      <c r="N36" s="1"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="1"/>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
-        <v>124</v>
-      </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1">
-        <v>154</v>
-      </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1">
-        <v>184</v>
-      </c>
-      <c r="J37" s="1"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1">
-        <v>214</v>
-      </c>
-      <c r="N37" s="1"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="1"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
-        <v>125</v>
-      </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1">
-        <v>155</v>
-      </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1">
-        <v>185</v>
-      </c>
-      <c r="J38" s="1"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1">
-        <v>215</v>
-      </c>
-      <c r="N38" s="1"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="1"/>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
-        <v>126</v>
-      </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1">
-        <v>156</v>
-      </c>
-      <c r="F39" s="1"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1">
-        <v>186</v>
-      </c>
-      <c r="J39" s="1"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1">
-        <v>216</v>
-      </c>
-      <c r="N39" s="1"/>
-      <c r="O39" s="4"/>
-      <c r="P39" s="1"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
-        <v>127</v>
-      </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1">
-        <v>157</v>
-      </c>
-      <c r="F40" s="1"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1">
-        <v>187</v>
-      </c>
-      <c r="J40" s="1"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1">
-        <v>217</v>
-      </c>
-      <c r="N40" s="1"/>
-      <c r="O40" s="4"/>
-      <c r="P40" s="1"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
-        <v>128</v>
-      </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1">
-        <v>158</v>
-      </c>
-      <c r="F41" s="1"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1">
-        <v>188</v>
-      </c>
-      <c r="J41" s="1"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1">
-        <v>218</v>
-      </c>
-      <c r="N41" s="1"/>
-      <c r="O41" s="4"/>
-      <c r="P41" s="1"/>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
-        <v>129</v>
-      </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1">
-        <v>159</v>
-      </c>
-      <c r="F42" s="1"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1">
-        <v>189</v>
-      </c>
-      <c r="J42" s="1"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1">
-        <v>219</v>
-      </c>
-      <c r="N42" s="1"/>
-      <c r="O42" s="4"/>
-      <c r="P42" s="1"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
-        <v>130</v>
-      </c>
-      <c r="B43" s="3"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1">
-        <v>160</v>
-      </c>
-      <c r="F43" s="1"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1">
-        <v>190</v>
-      </c>
-      <c r="J43" s="1"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1">
-        <v>220</v>
-      </c>
-      <c r="N43" s="1"/>
-      <c r="O43" s="4"/>
-      <c r="P43" s="1"/>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
-        <v>131</v>
-      </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1">
-        <v>161</v>
-      </c>
-      <c r="F44" s="1"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1">
-        <v>191</v>
-      </c>
-      <c r="J44" s="1"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1">
-        <v>221</v>
-      </c>
-      <c r="N44" s="1"/>
-      <c r="O44" s="4"/>
-      <c r="P44" s="1"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
-        <v>132</v>
-      </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1">
-        <v>162</v>
-      </c>
-      <c r="F45" s="1"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1">
-        <v>192</v>
-      </c>
-      <c r="J45" s="1"/>
-      <c r="K45" s="4"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1">
-        <v>222</v>
-      </c>
-      <c r="N45" s="1"/>
-      <c r="O45" s="4"/>
-      <c r="P45" s="1"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
-        <v>133</v>
-      </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1">
-        <v>163</v>
-      </c>
-      <c r="F46" s="1"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1">
-        <v>193</v>
-      </c>
-      <c r="J46" s="1"/>
-      <c r="K46" s="4"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1">
-        <v>223</v>
-      </c>
-      <c r="N46" s="1"/>
-      <c r="O46" s="4"/>
-      <c r="P46" s="1"/>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
-        <v>134</v>
-      </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1">
-        <v>164</v>
-      </c>
-      <c r="F47" s="1"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1">
-        <v>194</v>
-      </c>
-      <c r="J47" s="1"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1">
-        <v>224</v>
-      </c>
-      <c r="N47" s="1"/>
-      <c r="O47" s="4"/>
-      <c r="P47" s="1"/>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
-        <v>135</v>
-      </c>
-      <c r="B48" s="3"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1">
-        <v>165</v>
-      </c>
-      <c r="F48" s="1"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1">
-        <v>195</v>
-      </c>
-      <c r="J48" s="1"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1">
-        <v>225</v>
-      </c>
-      <c r="N48" s="1"/>
-      <c r="O48" s="4"/>
-      <c r="P48" s="1"/>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
-        <v>136</v>
-      </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1">
-        <v>166</v>
-      </c>
-      <c r="F49" s="1"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1">
-        <v>196</v>
-      </c>
-      <c r="J49" s="1"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1">
-        <v>226</v>
-      </c>
-      <c r="N49" s="1"/>
-      <c r="O49" s="4"/>
-      <c r="P49" s="1"/>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
-        <v>137</v>
-      </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1">
-        <v>167</v>
-      </c>
-      <c r="F50" s="1"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1">
-        <v>197</v>
-      </c>
-      <c r="J50" s="1"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="1"/>
-      <c r="M50" s="1">
-        <v>227</v>
-      </c>
-      <c r="N50" s="1"/>
-      <c r="O50" s="4"/>
-      <c r="P50" s="1"/>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
-        <v>138</v>
-      </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1">
-        <v>168</v>
-      </c>
-      <c r="F51" s="1"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1">
-        <v>198</v>
-      </c>
-      <c r="J51" s="1"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="1"/>
-      <c r="M51" s="1">
-        <v>228</v>
-      </c>
-      <c r="N51" s="1"/>
-      <c r="O51" s="4"/>
-      <c r="P51" s="1"/>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
-        <v>139</v>
-      </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1">
-        <v>169</v>
-      </c>
-      <c r="F52" s="1"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1">
-        <v>199</v>
-      </c>
-      <c r="J52" s="1"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1">
-        <v>229</v>
-      </c>
-      <c r="N52" s="1"/>
-      <c r="O52" s="4"/>
-      <c r="P52" s="1"/>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
-        <v>140</v>
-      </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1">
-        <v>170</v>
-      </c>
-      <c r="F53" s="1"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1">
-        <v>200</v>
-      </c>
-      <c r="J53" s="1"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="1"/>
-      <c r="M53" s="1">
-        <v>230</v>
-      </c>
-      <c r="N53" s="1"/>
-      <c r="O53" s="4"/>
-      <c r="P53" s="1"/>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
-        <v>141</v>
-      </c>
-      <c r="B54" s="3"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1">
-        <v>171</v>
-      </c>
-      <c r="F54" s="1"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1">
-        <v>201</v>
-      </c>
-      <c r="J54" s="1"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="1"/>
-      <c r="M54" s="1">
-        <v>231</v>
-      </c>
-      <c r="N54" s="1"/>
-      <c r="O54" s="4"/>
-      <c r="P54" s="1"/>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
-        <v>142</v>
-      </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1">
-        <v>172</v>
-      </c>
-      <c r="F55" s="1"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1">
-        <v>202</v>
-      </c>
-      <c r="J55" s="1"/>
-      <c r="K55" s="4"/>
-      <c r="L55" s="1"/>
-      <c r="M55" s="1">
-        <v>232</v>
-      </c>
-      <c r="N55" s="1"/>
-      <c r="O55" s="4"/>
-      <c r="P55" s="1"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
-        <v>143</v>
-      </c>
-      <c r="B56" s="3"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1">
-        <v>173</v>
-      </c>
-      <c r="F56" s="1"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1">
-        <v>203</v>
-      </c>
-      <c r="J56" s="1"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="1"/>
-      <c r="M56" s="1">
-        <v>233</v>
-      </c>
-      <c r="N56" s="1"/>
-      <c r="O56" s="4"/>
-      <c r="P56" s="1"/>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
-        <v>144</v>
-      </c>
-      <c r="B57" s="3"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1">
-        <v>174</v>
-      </c>
-      <c r="F57" s="1"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1">
-        <v>204</v>
-      </c>
-      <c r="J57" s="1"/>
-      <c r="K57" s="4"/>
-      <c r="L57" s="1"/>
-      <c r="M57" s="1">
-        <v>234</v>
-      </c>
-      <c r="N57" s="1"/>
-      <c r="O57" s="4"/>
-      <c r="P57" s="1"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
-        <v>145</v>
-      </c>
-      <c r="B58" s="3"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1">
-        <v>175</v>
-      </c>
-      <c r="F58" s="1"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1">
-        <v>205</v>
-      </c>
-      <c r="J58" s="1"/>
-      <c r="K58" s="4"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="1">
-        <v>235</v>
-      </c>
-      <c r="N58" s="1"/>
-      <c r="O58" s="4"/>
-      <c r="P58" s="1"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
-        <v>146</v>
-      </c>
-      <c r="B59" s="3"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="1"/>
-      <c r="E59" s="1">
-        <v>176</v>
-      </c>
-      <c r="F59" s="1"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1">
-        <v>206</v>
-      </c>
-      <c r="J59" s="1"/>
-      <c r="K59" s="4"/>
-      <c r="L59" s="1"/>
-      <c r="M59" s="1">
-        <v>236</v>
-      </c>
-      <c r="N59" s="1"/>
-      <c r="O59" s="4"/>
-      <c r="P59" s="1"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
-        <v>147</v>
-      </c>
-      <c r="B60" s="3"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1">
-        <v>177</v>
-      </c>
-      <c r="F60" s="1"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1">
-        <v>207</v>
-      </c>
-      <c r="J60" s="1"/>
-      <c r="K60" s="4"/>
-      <c r="L60" s="1"/>
-      <c r="M60" s="1">
-        <v>237</v>
-      </c>
-      <c r="N60" s="1"/>
-      <c r="O60" s="4"/>
-      <c r="P60" s="1"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
-        <v>148</v>
-      </c>
-      <c r="B61" s="3"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="1"/>
-      <c r="E61" s="1">
-        <v>178</v>
-      </c>
-      <c r="F61" s="1"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1">
-        <v>208</v>
-      </c>
-      <c r="J61" s="1"/>
-      <c r="K61" s="4"/>
-      <c r="L61" s="1"/>
-      <c r="M61" s="1">
-        <v>238</v>
-      </c>
-      <c r="N61" s="1"/>
-      <c r="O61" s="4"/>
-      <c r="P61" s="1"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
-        <v>149</v>
-      </c>
-      <c r="B62" s="3"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1">
-        <v>179</v>
-      </c>
-      <c r="F62" s="1"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1">
-        <v>209</v>
-      </c>
-      <c r="J62" s="1"/>
-      <c r="K62" s="4"/>
-      <c r="L62" s="1"/>
-      <c r="M62" s="1">
-        <v>239</v>
-      </c>
-      <c r="N62" s="1"/>
-      <c r="O62" s="4"/>
-      <c r="P62" s="1"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A63" s="1">
-        <v>150</v>
-      </c>
-      <c r="B63" s="3"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="1"/>
-      <c r="E63" s="1">
-        <v>180</v>
-      </c>
-      <c r="F63" s="1"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1">
-        <v>210</v>
-      </c>
-      <c r="J63" s="1"/>
-      <c r="K63" s="4"/>
-      <c r="L63" s="1"/>
-      <c r="M63" s="1">
-        <v>240</v>
-      </c>
-      <c r="N63" s="1"/>
-      <c r="O63" s="4"/>
-      <c r="P63" s="1"/>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C64" s="4"/>
-      <c r="D64" s="1"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
-        <v>241</v>
-      </c>
-      <c r="B65" s="3"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="1"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
-        <v>242</v>
-      </c>
-      <c r="B66" s="3"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="1"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
-        <v>243</v>
-      </c>
-      <c r="B67" s="3"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="1"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
-        <v>244</v>
-      </c>
-      <c r="B68" s="3"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="1"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
-        <v>245</v>
-      </c>
-      <c r="B69" s="3"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="1"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
-        <v>246</v>
-      </c>
-      <c r="B70" s="3"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="1"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
-        <v>247</v>
-      </c>
-      <c r="B71" s="3"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="1"/>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
-        <v>248</v>
-      </c>
-      <c r="B72" s="3"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="1"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
-        <v>249</v>
-      </c>
-      <c r="B73" s="3"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="1"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="1">
-        <v>250</v>
-      </c>
-      <c r="B74" s="3"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="1"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="1">
-        <v>251</v>
-      </c>
-      <c r="B75" s="3"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="1"/>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="1">
-        <v>252</v>
-      </c>
-      <c r="B76" s="3"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="1"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="1">
-        <v>253</v>
-      </c>
-      <c r="B77" s="3"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="1"/>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="1">
-        <v>254</v>
-      </c>
-      <c r="B78" s="3"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="1"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="1">
-        <v>255</v>
-      </c>
-      <c r="B79" s="3"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="1"/>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="1">
-        <v>256</v>
-      </c>
-      <c r="B80" s="3"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="1"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="1">
-        <v>257</v>
-      </c>
-      <c r="B81" s="3"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="1"/>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="1">
-        <v>258</v>
-      </c>
-      <c r="B82" s="3"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="1"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="1">
-        <v>259</v>
-      </c>
-      <c r="B83" s="3"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="1"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="1">
-        <v>260</v>
-      </c>
-      <c r="B84" s="3"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="1"/>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="1">
-        <v>261</v>
-      </c>
-      <c r="B85" s="3"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="1"/>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
-        <v>262</v>
-      </c>
-      <c r="B86" s="3"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="1"/>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="1">
-        <v>263</v>
-      </c>
-      <c r="B87" s="3"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="1"/>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="1">
-        <v>264</v>
-      </c>
-      <c r="B88" s="3"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="1"/>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="1">
-        <v>265</v>
-      </c>
-      <c r="B89" s="3"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="1"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="1">
-        <v>266</v>
-      </c>
-      <c r="B90" s="3"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="1"/>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="1">
-        <v>267</v>
-      </c>
-      <c r="B91" s="3"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="1"/>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="1">
-        <v>268</v>
-      </c>
-      <c r="B92" s="3"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="1"/>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="1">
-        <v>269</v>
-      </c>
-      <c r="B93" s="3"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="1"/>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="1">
-        <v>270</v>
-      </c>
-      <c r="B94" s="3"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="1"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>

--- a/LoanOfficer-A/2023/147 sheenarani.xlsx
+++ b/LoanOfficer-A/2023/147 sheenarani.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'MD50000.15-DEC'!$A$3:$N$32</definedName>
   </definedNames>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>5600</v>
+        <v>8400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>18400</v>
+        <v>15600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -886,9 +886,15 @@
       <c r="E3" s="1">
         <v>31</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G3" s="4">
+        <v>200</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
       <c r="I3" s="1">
         <v>61</v>
       </c>
@@ -918,9 +924,15 @@
       <c r="E4" s="1">
         <v>32</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G4" s="4">
+        <v>200</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
       <c r="I4" s="1">
         <v>62</v>
       </c>
@@ -950,9 +962,15 @@
       <c r="E5" s="1">
         <v>33</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="1"/>
+      <c r="F5" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G5" s="4">
+        <v>200</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
       <c r="I5" s="1">
         <v>63</v>
       </c>
@@ -982,9 +1000,15 @@
       <c r="E6" s="1">
         <v>34</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="1"/>
+      <c r="F6" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G6" s="4">
+        <v>200</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
       <c r="I6" s="1">
         <v>64</v>
       </c>
@@ -1014,9 +1038,15 @@
       <c r="E7" s="1">
         <v>35</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="1"/>
+      <c r="F7" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G7" s="4">
+        <v>200</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
       <c r="I7" s="1">
         <v>65</v>
       </c>
@@ -1046,9 +1076,15 @@
       <c r="E8" s="1">
         <v>36</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="1"/>
+      <c r="F8" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G8" s="4">
+        <v>200</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
       <c r="I8" s="1">
         <v>66</v>
       </c>
@@ -1078,9 +1114,15 @@
       <c r="E9" s="1">
         <v>37</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="1"/>
+      <c r="F9" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G9" s="4">
+        <v>200</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
       <c r="I9" s="1">
         <v>67</v>
       </c>
@@ -1110,9 +1152,15 @@
       <c r="E10" s="1">
         <v>38</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="1"/>
+      <c r="F10" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G10" s="4">
+        <v>200</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
       <c r="I10" s="1">
         <v>68</v>
       </c>
@@ -1142,9 +1190,15 @@
       <c r="E11" s="1">
         <v>39</v>
       </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="1"/>
+      <c r="F11" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G11" s="4">
+        <v>200</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
       <c r="I11" s="1">
         <v>69</v>
       </c>
@@ -1174,9 +1228,15 @@
       <c r="E12" s="1">
         <v>40</v>
       </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="1"/>
+      <c r="F12" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G12" s="4">
+        <v>200</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
       <c r="I12" s="1">
         <v>70</v>
       </c>
@@ -1206,9 +1266,15 @@
       <c r="E13" s="1">
         <v>41</v>
       </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="1"/>
+      <c r="F13" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G13" s="4">
+        <v>200</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
       <c r="I13" s="1">
         <v>71</v>
       </c>
@@ -1238,9 +1304,15 @@
       <c r="E14" s="1">
         <v>42</v>
       </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="1"/>
+      <c r="F14" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G14" s="4">
+        <v>200</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
       <c r="I14" s="1">
         <v>72</v>
       </c>
@@ -1770,9 +1842,15 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="1"/>
+      <c r="B31" s="3">
+        <v>46019</v>
+      </c>
+      <c r="C31" s="4">
+        <v>200</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
       <c r="E31" s="1">
         <v>59</v>
       </c>
@@ -1796,9 +1874,15 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="1"/>
+      <c r="B32" s="3">
+        <v>46019</v>
+      </c>
+      <c r="C32" s="4">
+        <v>200</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
       <c r="E32" s="1">
         <v>60</v>
       </c>
